--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/ozet_tablosu.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/ozet_tablosu.xlsx
@@ -1256,7 +1256,7 @@
       <c r="D1" s="35" t="n"/>
       <c r="E1" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026 / 0346 </t>
+          <t xml:space="preserve">2026 / 0298 </t>
         </is>
       </c>
       <c r="F1" s="37" t="n"/>
@@ -1272,7 +1272,7 @@
       <c r="D2" s="13" t="n"/>
       <c r="E2" s="19" t="inlineStr">
         <is>
-          <t>YDD R0 06 08 2026 1 MX 1 70 25 114</t>
+          <t>YDD R0 21 09 2026 1 MX 1 76 23 112</t>
         </is>
       </c>
       <c r="F2" s="39" t="n"/>
@@ -1288,7 +1288,7 @@
       <c r="D3" s="13" t="n"/>
       <c r="E3" s="40" t="inlineStr">
         <is>
-          <t>Acme Endüstri A.Ş.</t>
+          <t xml:space="preserve">Acme Endüstri A.Ş.	</t>
         </is>
       </c>
       <c r="F3" s="39" t="n"/>
@@ -1359,7 +1359,7 @@
       <c r="C7" s="43" t="n"/>
       <c r="D7" s="44" t="n"/>
       <c r="E7" s="47" t="n">
-        <v>70</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="F7" s="48" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
       <c r="C8" s="43" t="n"/>
       <c r="D8" s="44" t="n"/>
       <c r="E8" s="47" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="F8" s="48" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       <c r="C9" s="43" t="n"/>
       <c r="D9" s="44" t="n"/>
       <c r="E9" s="47" t="n">
-        <v>5.83</v>
+        <v>6.31</v>
       </c>
       <c r="F9" s="48" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       <c r="C10" s="43" t="n"/>
       <c r="D10" s="44" t="n"/>
       <c r="E10" s="49" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10" s="48" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       <c r="C12" s="43" t="n"/>
       <c r="D12" s="44" t="n"/>
       <c r="E12" s="47" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="F12" s="48" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       <c r="C14" s="43" t="n"/>
       <c r="D14" s="44" t="n"/>
       <c r="E14" s="49" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F14" s="48" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
       <c r="C17" s="43" t="n"/>
       <c r="D17" s="44" t="n"/>
       <c r="E17" s="49" t="n">
-        <v>752.4</v>
+        <v>739.2</v>
       </c>
       <c r="F17" s="48" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       <c r="C18" s="43" t="n"/>
       <c r="D18" s="44" t="n"/>
       <c r="E18" s="49" t="n">
-        <v>752.4</v>
+        <v>739.2</v>
       </c>
       <c r="F18" s="48" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B19" s="42" t="inlineStr">
         <is>
-          <t>Lamella Seperatör LS 15 Son Çöktürme Tankı</t>
+          <t>Lamella Seperatör LS 30 Son Çöktürme Tankı</t>
         </is>
       </c>
       <c r="C19" s="43" t="n"/>
@@ -1639,13 +1639,13 @@
       </c>
       <c r="B20" s="42" t="inlineStr">
         <is>
-          <t>1 Adet Lamella Seperatör LS 15 Son Çöktürme Tankı</t>
+          <t>1 Adet Lamella Seperatör LS 30 Son Çöktürme Tankı</t>
         </is>
       </c>
       <c r="C20" s="43" t="n"/>
       <c r="D20" s="44" t="n"/>
       <c r="E20" s="49" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F20" s="48" t="inlineStr">
         <is>
@@ -1661,13 +1661,13 @@
       </c>
       <c r="B21" s="42" t="inlineStr">
         <is>
-          <t>Lamella Seperatör LS 15 Son Çöktürme Tankı Toplam Yüzey Alanı</t>
+          <t>Lamella Seperatör LS 30 Son Çöktürme Tankı Toplam Yüzey Alanı</t>
         </is>
       </c>
       <c r="C21" s="43" t="n"/>
       <c r="D21" s="44" t="n"/>
       <c r="E21" s="49" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F21" s="48" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D29" s="54" t="inlineStr">
         <is>
-          <t>LS 15 Lamella Seperatör Son Çöktürme Tankı</t>
+          <t>LS 30 Lamella Seperatör Son Çöktürme Tankı</t>
         </is>
       </c>
       <c r="E29" s="43" t="n"/>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="D30" s="54" t="inlineStr">
         <is>
-          <t>LS 15 Lamella Seperatör Son Çöktürme Tankı Çamur Pompası</t>
+          <t>LS 30 Lamella Seperatör Son Çöktürme Tankı Çamur Pompası</t>
         </is>
       </c>
       <c r="E30" s="43" t="n"/>
